--- a/assets/xlsx/pages.unified.xlsx
+++ b/assets/xlsx/pages.unified.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="31">
   <si>
     <t>dir_path</t>
   </si>
@@ -83,6 +83,30 @@
     <t>1,2</t>
   </si>
   <si>
+    <t>topics</t>
+  </si>
+  <si>
+    <t>专题导航 - 正协导航</t>
+  </si>
+  <si>
+    <t>正协导航全部专题导航：政务导航、搜索工具、政协专题等，一站直达各类导航。</t>
+  </si>
+  <si>
+    <t>专题导航,正协导航,政务导航,搜索工具,政协</t>
+  </si>
+  <si>
+    <t>topics/search</t>
+  </si>
+  <si>
+    <t>搜索工具 - 正协导航</t>
+  </si>
+  <si>
+    <t>正协导航搜索工具专题：聚合搜索引擎导航，在站内一键调用 Google、必应、百度、AI 对话、学术搜索等检索工具，方便快速查找。</t>
+  </si>
+  <si>
+    <t>搜索工具,搜索引擎,聚合搜索,Google,必应,百度,隐私搜索,学术搜索,AI对话</t>
+  </si>
+  <si>
     <t>topics/gov</t>
   </si>
   <si>
@@ -96,30 +120,6 @@
   </si>
   <si>
     <t>本频道汇集两类权威政务官方入口：一是人民代表大会系统——从全国人民代表大会到地方各级人大；二是政务机构系统——国务院、国家政务服务平台及主要组成部门。所有链接均指向经核实的官方域名，帮你少走弯路、直达源头。</t>
-  </si>
-  <si>
-    <t>topics/search</t>
-  </si>
-  <si>
-    <t>搜索工具 - 正协导航</t>
-  </si>
-  <si>
-    <t>正协导航搜索工具专题：聚合搜索引擎导航，在站内一键调用 Google、必应、百度、AI 对话、学术搜索等检索工具，方便快速查找。</t>
-  </si>
-  <si>
-    <t>搜索工具,搜索引擎,聚合搜索,Google,必应,百度,隐私搜索,学术搜索,AI对话</t>
-  </si>
-  <si>
-    <t>topics</t>
-  </si>
-  <si>
-    <t>专题导航 - 正协导航</t>
-  </si>
-  <si>
-    <t>正协导航全部专题导航：政务导航、搜索工具、政协专题等，一站直达各类导航。</t>
-  </si>
-  <si>
-    <t>专题导航,正协导航,政务导航,搜索工具,政协</t>
   </si>
 </sst>
 </file>
@@ -132,14 +132,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -595,148 +588,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1091,10 +1084,10 @@
   <dimension ref="A1:K5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="17.25" customWidth="1"/>
+    <col min="1" max="1" width="14.5" customWidth="1"/>
     <col min="2" max="2" width="20.75" customWidth="1"/>
     <col min="3" max="3" width="21.5" customWidth="1"/>
-    <col min="5" max="5" width="14.5" customWidth="1"/>
+    <col min="5" max="5" width="19.75" customWidth="1"/>
     <col min="7" max="7" width="10.5" customWidth="1"/>
     <col min="8" max="8" width="5.875" customWidth="1"/>
     <col min="9" max="9" width="9.375" customWidth="1"/>
@@ -1181,18 +1174,13 @@
       <c r="D3" t="s">
         <v>21</v>
       </c>
-      <c r="E3" t="s">
-        <v>22</v>
-      </c>
       <c r="F3" t="s">
         <v>16</v>
       </c>
       <c r="G3" t="s">
         <v>16</v>
       </c>
-      <c r="H3" t="s">
-        <v>17</v>
-      </c>
+      <c r="H3"/>
       <c r="I3" t="s">
         <v>16</v>
       </c>
@@ -1202,16 +1190,16 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
         <v>23</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>24</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>25</v>
-      </c>
-      <c r="D4" t="s">
-        <v>26</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
@@ -1231,15 +1219,18 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s">
         <v>27</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>28</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>29</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>30</v>
       </c>
       <c r="F5" t="s">
